--- a/data/trans_orig/IP18B2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18B2-Estudios-trans_orig.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,23%</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3124,47 +3124,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>39,26%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>11,24%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>38,99%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2584</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3385,12 +3385,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>583</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>10834</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5256,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9281</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5306,12 +5306,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>14865</t>
+          <t>15097</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5341,12 +5341,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5536,12 +5536,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5571,12 +5571,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -6277,12 +6277,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6543,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -6955,12 +6955,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -7221,44 +7221,44 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
+          <t>3728</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>10,04%</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>46,29%</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
           <t>3886</t>
         </is>
       </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>48,26%</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
-          <t>3905</t>
-        </is>
-      </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
           <t>4,86%</t>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -7863,12 +7863,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8124,12 +8124,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8669,12 +8669,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4989</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -9332,12 +9332,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -9445,12 +9445,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9266</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10767,12 +10767,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>62,71%</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -11267,7 +11267,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11332,12 +11332,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12658,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -12853,7 +12853,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2350</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12918,12 +12918,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12933,12 +12933,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -13074,12 +13074,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13109,12 +13109,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13124,12 +13124,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13144,12 +13144,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>13219</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13531,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13576,12 +13576,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13596,12 +13596,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13611,12 +13611,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,24%</t>
         </is>
       </c>
     </row>
@@ -13639,12 +13639,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13654,12 +13654,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>756</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13689,12 +13689,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13709,12 +13709,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13724,12 +13724,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13807,7 +13807,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -13870,7 +13870,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -13955,7 +13955,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -14430,12 +14430,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14445,12 +14445,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14696,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14711,7 +14711,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -14952,12 +14952,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -14967,12 +14967,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15030,12 +15030,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15045,12 +15045,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15065,12 +15065,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15080,12 +15080,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -15260,12 +15260,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -15275,12 +15275,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -15310,12 +15310,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -15456,7 +15456,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -15486,12 +15486,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -15501,12 +15501,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -15521,12 +15521,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -15536,12 +15536,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -15903,12 +15903,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -15918,12 +15918,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -15973,12 +15973,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -15988,12 +15988,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -16016,12 +16016,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -16031,12 +16031,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -16086,12 +16086,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -16101,12 +16101,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -16671,7 +16671,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -16847,7 +16847,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -17264,7 +17264,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -17279,7 +17279,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -17407,12 +17407,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -17422,12 +17422,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -17442,12 +17442,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -17457,12 +17457,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -17602,12 +17602,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -17617,12 +17617,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -17637,12 +17637,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -17652,12 +17652,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -17672,12 +17672,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -17687,12 +17687,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -17755,7 +17755,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -17828,12 +17828,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -17843,12 +17843,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -17863,12 +17863,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -17878,12 +17878,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -17898,12 +17898,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>10759</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -17913,12 +17913,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -17946,7 +17946,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -18207,7 +18207,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -18257,7 +18257,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -18280,12 +18280,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7859</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -18295,12 +18295,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2713</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -18350,12 +18350,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -18365,12 +18365,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -18393,12 +18393,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -18408,12 +18408,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -18428,12 +18428,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>10671</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -18443,12 +18443,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -18463,12 +18463,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -18546,7 +18546,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3292</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -18885,7 +18885,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -18900,7 +18900,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -18935,7 +18935,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -18963,7 +18963,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -19071,12 +19071,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -19086,12 +19086,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -19111,7 +19111,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -19141,12 +19141,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -19156,12 +19156,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -19184,12 +19184,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -19199,12 +19199,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -19234,12 +19234,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -19254,12 +19254,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -19269,12 +19269,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -19450,7 +19450,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -19465,7 +19465,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -19485,7 +19485,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -19500,7 +19500,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -19563,7 +19563,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -19598,7 +19598,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -19636,12 +19636,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -19651,12 +19651,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -19706,12 +19706,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -19721,12 +19721,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -19749,12 +19749,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -19764,12 +19764,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -19784,12 +19784,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -19799,12 +19799,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>543</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -20521,12 +20521,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>62,45%</t>
         </is>
       </c>
     </row>
@@ -20667,7 +20667,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,48%</t>
         </is>
       </c>
     </row>
@@ -20780,7 +20780,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -20795,7 +20795,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -20865,7 +20865,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -21006,7 +21006,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -22136,7 +22136,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -22201,12 +22201,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>497</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -22216,12 +22216,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -22362,7 +22362,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -22432,7 +22432,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3632</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -22587,12 +22587,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>499</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -22602,12 +22602,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -22622,12 +22622,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -22637,12 +22637,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -22657,12 +22657,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -22672,12 +22672,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -22740,7 +22740,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4583</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -22813,12 +22813,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -22828,12 +22828,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -22848,12 +22848,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -22863,12 +22863,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -22883,12 +22883,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -22898,12 +22898,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -23129,7 +23129,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -23192,7 +23192,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -23207,7 +23207,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -23265,12 +23265,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -23280,12 +23280,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -23305,7 +23305,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -23320,7 +23320,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -23335,12 +23335,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -23350,12 +23350,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -23383,7 +23383,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -23418,7 +23418,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -23526,12 +23526,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -23541,12 +23541,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -23561,12 +23561,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -23576,12 +23576,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -23609,7 +23609,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -23644,7 +23644,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -23659,7 +23659,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -24056,12 +24056,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -24071,12 +24071,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -24126,12 +24126,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>750</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -24141,12 +24141,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -24174,7 +24174,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -24189,7 +24189,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -24209,7 +24209,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -24239,12 +24239,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -24254,12 +24254,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -24435,7 +24435,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -24450,7 +24450,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -24470,7 +24470,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -24485,7 +24485,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -24513,7 +24513,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -24528,7 +24528,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -24598,7 +24598,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -24734,12 +24734,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -24749,12 +24749,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -24769,12 +24769,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -24784,12 +24784,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -24804,12 +24804,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -24964,12 +24964,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -25034,12 +25034,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -25049,12 +25049,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3071</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -25210,7 +25210,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -25260,12 +25260,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -25275,12 +25275,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -25471,7 +25471,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -25491,7 +25491,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -25569,7 +25569,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -25604,7 +25604,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -25647,7 +25647,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -25662,7 +25662,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -25717,7 +25717,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -25795,7 +25795,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -25810,7 +25810,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -25830,7 +25830,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -25845,7 +25845,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -26508,7 +26508,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -26551,7 +26551,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -26566,7 +26566,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -26581,12 +26581,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -26596,12 +26596,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -26616,12 +26616,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -26631,12 +26631,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -26792,7 +26792,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -26812,7 +26812,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -26827,7 +26827,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -26847,7 +26847,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -27003,7 +27003,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -27073,7 +27073,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -27116,7 +27116,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -27146,12 +27146,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>812</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -27181,12 +27181,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7644</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -27196,12 +27196,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -27341,12 +27341,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -27356,12 +27356,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -27376,12 +27376,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -27391,12 +27391,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -27411,12 +27411,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -27426,12 +27426,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -27509,7 +27509,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -27544,7 +27544,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -27567,12 +27567,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -27582,12 +27582,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -27602,12 +27602,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>12967</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -27617,12 +27617,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -27637,12 +27637,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -27652,12 +27652,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -27798,7 +27798,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -27833,7 +27833,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -27863,12 +27863,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -27883,7 +27883,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -27911,7 +27911,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -27961,7 +27961,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -27976,12 +27976,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -28019,12 +28019,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -28034,12 +28034,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -28059,7 +28059,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -28074,7 +28074,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -28089,12 +28089,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -28104,12 +28104,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -28137,7 +28137,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -28152,7 +28152,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -28167,12 +28167,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -28182,12 +28182,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -28202,12 +28202,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -28217,12 +28217,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -28280,12 +28280,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -28295,12 +28295,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -28315,12 +28315,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -28330,12 +28330,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -28363,7 +28363,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -28398,7 +28398,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -28413,7 +28413,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -28428,12 +28428,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -28443,12 +28443,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -28810,12 +28810,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -28825,12 +28825,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -28850,7 +28850,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -28865,7 +28865,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -28880,12 +28880,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -28895,12 +28895,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -28923,12 +28923,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>581</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -28938,12 +28938,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -28958,12 +28958,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -28973,12 +28973,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -28993,12 +28993,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -29008,12 +29008,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -29169,7 +29169,7 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -29189,7 +29189,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -29224,7 +29224,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -29239,7 +29239,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -29262,12 +29262,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -29277,12 +29277,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -29317,7 +29317,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -29332,12 +29332,12 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -29347,12 +29347,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -29380,7 +29380,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -29450,7 +29450,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -29465,7 +29465,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -29488,12 +29488,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -29503,12 +29503,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -29523,12 +29523,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -29538,12 +29538,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -29558,12 +29558,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>6209</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -29573,12 +29573,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
